--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EL_PORVENIR</t>
+          <t>EL PORVENIR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>PIERRE SIMON LAPLACE COLLEGE</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.085369999999999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.00439</v>
-      </c>
-      <c r="I2" t="n">
-        <v>247</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.08537</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.00439</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1562 NUEVO HORIZONTE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.071490000000002</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.98944</v>
-      </c>
-      <c r="I3" t="n">
-        <v>290</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.071490000000002</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.98944</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1566 EL PILOTO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.082560000000003</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.00207</v>
-      </c>
-      <c r="I4" t="n">
-        <v>415</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.082560000000003</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.00207</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>1579 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.07578</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.00818</v>
-      </c>
-      <c r="I5" t="n">
-        <v>317</v>
-      </c>
-      <c r="J5" t="n">
-        <v>15</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.07578</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.00818</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>1580 GERARDO KUPPENS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.074999999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.9965</v>
-      </c>
-      <c r="I6" t="n">
-        <v>270</v>
-      </c>
-      <c r="J6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.075</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.9965</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>80026 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.08442</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.99584</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1525</v>
-      </c>
-      <c r="J7" t="n">
-        <v>65</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.08442</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.99584</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>80027 JOSE ABELARDO QUIÑONES GONZALES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.076725</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.99823499999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>759</v>
-      </c>
-      <c r="J8" t="n">
-        <v>32</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.076725</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.998235</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>80028 FRANCISCO DE ZELA</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.08362</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.99285999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>632</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.08362</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.99286</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>80029 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.087910000000003</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.99311</v>
-      </c>
-      <c r="I10" t="n">
-        <v>482</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.087910000000003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.99311</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>80030 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.08588</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.00876</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1034</v>
-      </c>
-      <c r="J11" t="n">
-        <v>48</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.08588</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.00876</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>80627 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.072480000000002</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.99433999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1843</v>
-      </c>
-      <c r="J12" t="n">
-        <v>72</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.072480000000002</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.99434</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>80756 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.0725</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.98987</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1395</v>
-      </c>
-      <c r="J13" t="n">
-        <v>60</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.0725</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.98987</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>80819 FRANCISCO LIZARZABURO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.080076</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.001113</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2586</v>
-      </c>
-      <c r="J14" t="n">
-        <v>101</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.080076</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.001113</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2586</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>80823 EL INDOAMERICANO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.07512</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.00637</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2270</v>
-      </c>
-      <c r="J15" t="n">
-        <v>93</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.07512</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.00637</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2270</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>81778 RAMIRO PRIALE</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.070029999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.0134</v>
-      </c>
-      <c r="I16" t="n">
-        <v>398</v>
-      </c>
-      <c r="J16" t="n">
-        <v>16</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.07003</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.0134</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>398</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.08527</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.00414000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>504</v>
-      </c>
-      <c r="J17" t="n">
-        <v>29</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.08527</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.00414</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>LA CARIDAD</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.07728</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.99951</v>
-      </c>
-      <c r="I18" t="n">
-        <v>718</v>
-      </c>
-      <c r="J18" t="n">
-        <v>31</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.07728</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.99951</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.066850000000002</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.98622</v>
-      </c>
-      <c r="I19" t="n">
-        <v>545</v>
-      </c>
-      <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.066850000000002</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.98622</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.08339</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.004054</v>
-      </c>
-      <c r="I20" t="n">
-        <v>379</v>
-      </c>
-      <c r="J20" t="n">
-        <v>22</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.08339</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.004054</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>SAN MATEO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.085179999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.99852</v>
-      </c>
-      <c r="I21" t="n">
-        <v>304</v>
-      </c>
-      <c r="J21" t="n">
-        <v>26</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.08518</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.99852</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>TERESA DE LOS ANGELES</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.084099999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.00183</v>
-      </c>
-      <c r="I22" t="n">
-        <v>572</v>
-      </c>
-      <c r="J22" t="n">
-        <v>30</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.0841</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.00183</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>1635</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.086</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.0112</v>
-      </c>
-      <c r="I23" t="n">
-        <v>43</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.086</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.0112</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>80831 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.07274</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.02037</v>
-      </c>
-      <c r="I24" t="n">
-        <v>873</v>
-      </c>
-      <c r="J24" t="n">
-        <v>43</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.07274</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.02037</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SEMILLITAS DE JESUS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.072050000000003</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.99642</v>
-      </c>
-      <c r="I25" t="n">
-        <v>239</v>
-      </c>
-      <c r="J25" t="n">
-        <v>21</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.072050000000003</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.99642</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>CASITA DE SORPRESAS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.08339</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.00141000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>243</v>
-      </c>
-      <c r="J26" t="n">
-        <v>17</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.08339</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.00141</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.080870000000003</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.00897999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>251</v>
-      </c>
-      <c r="J27" t="n">
-        <v>17</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.080870000000003</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.00898</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.087160000000003</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.99858999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>413</v>
-      </c>
-      <c r="J28" t="n">
-        <v>21</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.087160000000003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.99859</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>2200 EMILIA Y VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.065619999999999</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.98898</v>
-      </c>
-      <c r="I29" t="n">
-        <v>458</v>
-      </c>
-      <c r="J29" t="n">
-        <v>18</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.06562</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.98898</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>TERCER CIELO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.071529999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.99207</v>
-      </c>
-      <c r="I30" t="n">
-        <v>399</v>
-      </c>
-      <c r="J30" t="n">
-        <v>21</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.07153</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.99207</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>MIGUEL ANGEL BUONARROTI DEL PORVENIR</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.073320000000002</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.99249</v>
-      </c>
-      <c r="I31" t="n">
-        <v>217</v>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.073320000000002</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.99249</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.087339999999999</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.99861</v>
-      </c>
-      <c r="I32" t="n">
-        <v>271</v>
-      </c>
-      <c r="J32" t="n">
-        <v>17</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.08734</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.99861</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NOVA SCHOOL</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.07447</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.01085999999999</v>
-      </c>
-      <c r="I33" t="n">
-        <v>303</v>
-      </c>
-      <c r="J33" t="n">
-        <v>10</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.07447</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.01086</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>835901</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PIERRE SIMON LAPLACE COLLEGE</t>
+          <t>NOVA SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.08537</t>
+          <t>-8.07447</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.00439</t>
+          <t>-79.01086</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>252644</t>
+          <t>252776</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1562 NUEVO HORIZONTE</t>
+          <t>80819 FRANCISCO LIZARZABURO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.071490000000002</t>
+          <t>-8.080076</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.98944</t>
+          <t>-79.001113</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>252663</t>
+          <t>252644</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1566 EL PILOTO</t>
+          <t>1562 NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.082560000000003</t>
+          <t>-8.071490000000002</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.00207</t>
+          <t>-78.98944</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>252677</t>
+          <t>252682</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1579 CORAZON DEL NIÑO JESUS</t>
+          <t>1580 GERARDO KUPPENS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.07578</t>
+          <t>-8.075</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.00818</t>
+          <t>-78.9965</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>252682</t>
+          <t>58722</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1580 GERARDO KUPPENS</t>
+          <t>PIERRE SIMON LAPLACE COLLEGE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.075</t>
+          <t>-8.08537</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.9965</t>
+          <t>-79.00439</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>252700</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>80026 HORACIO ZEVALLOS GAMEZ</t>
+          <t>1579 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.08442</t>
+          <t>-8.07578</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.99584</t>
+          <t>-79.00818</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>252719</t>
+          <t>805329</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80027 JOSE ABELARDO QUIÑONES GONZALES</t>
+          <t>MIGUEL ANGEL BUONARROTI DEL PORVENIR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.076725</t>
+          <t>-8.073320000000002</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.998235</t>
+          <t>-78.99249</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>252724</t>
+          <t>252823</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>80028 FRANCISCO DE ZELA</t>
+          <t>81778 RAMIRO PRIALE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.08362</t>
+          <t>-8.07003</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.99286</t>
+          <t>-79.0134</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>398</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>252738</t>
+          <t>252663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80029 MARIANO MELGAR</t>
+          <t>1566 EL PILOTO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.087910000000003</t>
+          <t>-8.082560000000003</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.99311</t>
+          <t>-79.00207</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>252743</t>
+          <t>657343</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>80030 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>CASITA DE SORPRESAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.08588</t>
+          <t>-8.08339</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.00876</t>
+          <t>-79.00141</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>252757</t>
+          <t>658762</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80627 LEONCIO PRADO GUTIERREZ</t>
+          <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.072480000000002</t>
+          <t>-8.080870000000003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.99434</t>
+          <t>-79.00898</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>251</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>252762</t>
+          <t>831583</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80756 JOSE MARIA ARGUEDAS</t>
+          <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.0725</t>
+          <t>-8.08734</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.98987</t>
+          <t>-78.99861</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>252776</t>
+          <t>737321</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>80819 FRANCISCO LIZARZABURO</t>
+          <t>2200 EMILIA Y VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.080076</t>
+          <t>-8.06562</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.001113</t>
+          <t>-78.98898</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>252781</t>
+          <t>253163</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80823 EL INDOAMERICANO</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.07512</t>
+          <t>-8.086</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.00637</t>
+          <t>-79.0112</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>252823</t>
+          <t>252955</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>81778 RAMIRO PRIALE</t>
+          <t>VIRGEN DEL CARMEN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.07003</t>
+          <t>-8.066850000000002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.0134</t>
+          <t>-78.98622</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>545</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>252917</t>
+          <t>522820</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>SEMILLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.08527</t>
+          <t>-8.072050000000003</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.00414</t>
+          <t>-78.99642</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>252922</t>
+          <t>659605</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LA CARIDAD</t>
+          <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.07728</t>
+          <t>-8.087160000000003</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.99951</t>
+          <t>-78.99859</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>413</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>252955</t>
+          <t>783921</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VIRGEN DEL CARMEN</t>
+          <t>TERCER CIELO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.066850000000002</t>
+          <t>-8.07153</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.98622</t>
+          <t>-78.99207</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>399</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>253002</t>
+          <t>252738</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SAN MATEO</t>
+          <t>80029 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.08518</t>
+          <t>-8.087910000000003</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.99852</t>
+          <t>-78.99311</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>253021</t>
+          <t>253002</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TERESA DE LOS ANGELES</t>
+          <t>SAN MATEO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.0841</t>
+          <t>-8.08518</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.00183</t>
+          <t>-78.99852</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>304</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>253163</t>
+          <t>252917</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.086</t>
+          <t>-8.08527</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.0112</t>
+          <t>-79.00414</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>504</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>253224</t>
+          <t>252724</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80831 FRANCISCO BOLOGNESI</t>
+          <t>80028 FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.07274</t>
+          <t>-8.08362</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.02037</t>
+          <t>-78.99286</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>632</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>522820</t>
+          <t>253021</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE JESUS</t>
+          <t>TERESA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.072050000000003</t>
+          <t>-8.0841</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.99642</t>
+          <t>-79.00183</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>572</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>657343</t>
+          <t>252922</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASITA DE SORPRESAS</t>
+          <t>LA CARIDAD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.08339</t>
+          <t>-8.07728</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.00141</t>
+          <t>-78.99951</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>718</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>658762</t>
+          <t>252719</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA MISERICORDIA</t>
+          <t>80027 JOSE ABELARDO QUIÑONES GONZALES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.080870000000003</t>
+          <t>-8.076725</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.00898</t>
+          <t>-78.998235</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>759</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>659605</t>
+          <t>253224</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SANTA RITA DE JESUS</t>
+          <t>80831 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.087160000000003</t>
+          <t>-8.07274</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.99859</t>
+          <t>-79.02037</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>873</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>737321</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2200 EMILIA Y VICTORIA BARCIA BONIFFATTI</t>
+          <t>80030 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.06562</t>
+          <t>-8.08588</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.98898</t>
+          <t>-79.00876</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>783921</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TERCER CIELO</t>
+          <t>80756 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.07153</t>
+          <t>-8.0725</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.99207</t>
+          <t>-78.98987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>805329</t>
+          <t>252700</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL BUONARROTI DEL PORVENIR</t>
+          <t>80026 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.073320000000002</t>
+          <t>-8.08442</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.99249</t>
+          <t>-78.99584</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>831583</t>
+          <t>252757</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SANTA RITA DE JESUS</t>
+          <t>80627 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.08734</t>
+          <t>-8.072480000000002</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.99861</t>
+          <t>-78.99434</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>835901</t>
+          <t>252781</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NOVA SCHOOL</t>
+          <t>80823 EL INDOAMERICANO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.07447</t>
+          <t>-8.07512</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.01086</t>
+          <t>-79.00637</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.071490000000002</t>
+          <t>-8.07149</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.073320000000002</t>
+          <t>-8.07332</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.082560000000003</t>
+          <t>-8.08256</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.080870000000003</t>
+          <t>-8.08087</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.066850000000002</t>
+          <t>-8.06685</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.072050000000003</t>
+          <t>-8.07205</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.087160000000003</t>
+          <t>-8.08716</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.087910000000003</t>
+          <t>-8.08791</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.072480000000002</t>
+          <t>-8.07248</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-8.07447</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-79.01086</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>252776</t>
+          <t>831583</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>80819 FRANCISCO LIZARZABURO</t>
+          <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.080076</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.001113</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>-8.08734</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>-78.99861</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>252644</t>
+          <t>805329</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1562 NUEVO HORIZONTE</t>
+          <t>MIGUEL ANGEL BUONARROTI DEL PORVENIR</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.07149</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.98944</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-8.073320000000002</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-78.99249</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>252682</t>
+          <t>783921</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1580 GERARDO KUPPENS</t>
+          <t>TERCER CIELO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.075</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.9965</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-8.07153</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-78.99207</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58722</t>
+          <t>737321</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PIERRE SIMON LAPLACE COLLEGE</t>
+          <t>2200 EMILIA Y VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.08537</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.00439</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>-8.06562</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.98898</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>252677</t>
+          <t>659605</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1579 CORAZON DEL NIÑO JESUS</t>
+          <t>SANTA RITA DE JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.07578</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.00818</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-8.087160000000003</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.99859</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>805329</t>
+          <t>658762</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL BUONARROTI DEL PORVENIR</t>
+          <t>SEÑOR DE LA MISERICORDIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.07332</t>
+          <t>251</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.99249</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-8.080870000000003</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.00898</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>252823</t>
+          <t>657343</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81778 RAMIRO PRIALE</t>
+          <t>CASITA DE SORPRESAS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.07003</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.0134</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>-8.08339</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.00141</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>252663</t>
+          <t>522820</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1566 EL PILOTO</t>
+          <t>SEMILLITAS DE JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.08256</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.00207</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-8.072050000000003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.99642</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>657343</t>
+          <t>253224</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASITA DE SORPRESAS</t>
+          <t>80831 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.08339</t>
+          <t>873</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.00141</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-8.07274</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.02037</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>658762</t>
+          <t>253163</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA MISERICORDIA</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.08087</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.00898</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>-8.086</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.0112</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>831583</t>
+          <t>253021</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA RITA DE JESUS</t>
+          <t>TERESA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.08734</t>
+          <t>572</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.99861</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-8.0841</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.00183</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>737321</t>
+          <t>253002</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2200 EMILIA Y VICTORIA BARCIA BONIFFATTI</t>
+          <t>SAN MATEO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.06562</t>
+          <t>304</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.98898</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-8.08518</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.99852</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>253163</t>
+          <t>252984</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1635</t>
+          <t>JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.086</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.0112</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-8.08339</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-79.004054</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.06685</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-8.066850000000002</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>-78.98622</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>522820</t>
+          <t>252922</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SEMILLITAS DE JESUS</t>
+          <t>LA CARIDAD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.07205</t>
+          <t>718</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.99642</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-8.07728</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.99951</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>659605</t>
+          <t>252917</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA RITA DE JESUS</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.08716</t>
+          <t>504</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.99859</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>-8.08527</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.00414</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>783921</t>
+          <t>252823</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TERCER CIELO</t>
+          <t>81778 RAMIRO PRIALE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.07153</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.99207</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-8.07003</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.0134</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>252984</t>
+          <t>252781</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JESUS DE NAZARETH</t>
+          <t>80823 EL INDOAMERICANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.08339</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.004054</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-8.07512</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.00637</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>252738</t>
+          <t>252776</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80029 MARIANO MELGAR</t>
+          <t>80819 FRANCISCO LIZARZABURO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.08791</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.99311</t>
+          <t>101</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-8.080076</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.001113</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>253002</t>
+          <t>252762</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN MATEO</t>
+          <t>80756 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.08518</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.99852</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>-8.0725</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.98987</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>252917</t>
+          <t>252757</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>80627 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.08527</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.00414</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>-8.072480000000002</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.99434</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>252724</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80028 FRANCISCO DE ZELA</t>
+          <t>80030 VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.08362</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.99286</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>-8.08588</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.00876</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>253021</t>
+          <t>252738</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TERESA DE LOS ANGELES</t>
+          <t>80029 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.0841</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.00183</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>-8.087910000000003</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.99311</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>252922</t>
+          <t>252724</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LA CARIDAD</t>
+          <t>80028 FRANCISCO DE ZELA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.07728</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.99951</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>-8.08362</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.99286</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>-8.076725</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>-78.998235</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>253224</t>
+          <t>252700</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>80831 FRANCISCO BOLOGNESI</t>
+          <t>80026 HORACIO ZEVALLOS GAMEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.07274</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.02037</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>-8.08442</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.99584</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>252743</t>
+          <t>252682</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80030 VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>1580 GERARDO KUPPENS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.08588</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.00876</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>-8.075</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-78.9965</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>252762</t>
+          <t>252677</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>80756 JOSE MARIA ARGUEDAS</t>
+          <t>1579 CORAZON DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.0725</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.98987</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>-8.07578</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-79.00818</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>252700</t>
+          <t>252663</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>80026 HORACIO ZEVALLOS GAMEZ</t>
+          <t>1566 EL PILOTO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.08442</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.99584</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>-8.082560000000003</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-79.00207</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>252757</t>
+          <t>252644</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>80627 LEONCIO PRADO GUTIERREZ</t>
+          <t>1562 NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.07248</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.99434</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>-8.071490000000002</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>-78.98944</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>252781</t>
+          <t>058722</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>80823 EL INDOAMERICANO</t>
+          <t>PIERRE SIMON LAPLACE COLLEGE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.07512</t>
+          <t>247</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.00637</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>-8.08537</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>-79.00439</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-EL_PORVENIR.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
